--- a/TestCase web page on java script.xlsx
+++ b/TestCase web page on java script.xlsx
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>Pass / Fail / Not executed / Suspended</t>
-  </si>
-  <si>
-    <t>TC_Practical_Web page</t>
   </si>
   <si>
     <t>1.0</t>
@@ -222,6 +219,9 @@
   </si>
   <si>
     <t>Test the Login Functionality of Web page on Java Script.</t>
+  </si>
+  <si>
+    <t>TC_Practical_4</t>
   </si>
 </sst>
 </file>
@@ -1011,14 +1011,14 @@
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G1" s="40"/>
       <c r="H1" s="40"/>
@@ -1046,14 +1046,14 @@
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2" s="27"/>
       <c r="H2" s="46" t="s">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="I2" s="27"/>
       <c r="J2" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -1179,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="27"/>
@@ -1332,7 +1332,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
@@ -1361,7 +1361,7 @@
     <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
       <c r="B12" s="37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" s="36"/>
       <c r="D12" s="36"/>
@@ -1456,11 +1456,11 @@
         <v>1</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="42"/>
       <c r="D15" s="29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="27"/>
       <c r="F15" s="25"/>
@@ -1489,11 +1489,11 @@
         <v>2</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="27"/>
       <c r="D16" s="29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="25"/>
@@ -1522,11 +1522,11 @@
         <v>3</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="27"/>
       <c r="D17" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="25"/>
@@ -1555,11 +1555,11 @@
         <v>4</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" s="27"/>
       <c r="F18" s="25"/>
@@ -1588,11 +1588,11 @@
         <v>5</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="25"/>
@@ -1621,11 +1621,11 @@
         <v>6</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="27"/>
       <c r="D20" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E20" s="27"/>
       <c r="F20" s="25"/>
@@ -1654,11 +1654,11 @@
         <v>7</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" s="27"/>
       <c r="D21" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" s="27"/>
       <c r="F21" s="25"/>
@@ -1687,11 +1687,11 @@
         <v>8</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="27"/>
       <c r="D22" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" s="27"/>
       <c r="F22" s="25"/>
@@ -1720,11 +1720,11 @@
         <v>9</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23" s="27"/>
       <c r="D23" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="25"/>
@@ -1753,11 +1753,11 @@
         <v>10</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="27"/>
       <c r="D24" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="25"/>
@@ -1786,11 +1786,11 @@
         <v>11</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" s="27"/>
       <c r="D25" s="29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E25" s="27"/>
       <c r="F25" s="25"/>
@@ -1819,11 +1819,11 @@
         <v>12</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" s="27"/>
       <c r="D26" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" s="27"/>
       <c r="F26" s="25"/>
@@ -1852,11 +1852,11 @@
         <v>13</v>
       </c>
       <c r="B27" s="29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="27"/>
       <c r="D27" s="29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="25"/>
@@ -1885,11 +1885,11 @@
         <v>14</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="27"/>
       <c r="D28" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="25"/>
@@ -1918,11 +1918,11 @@
         <v>15</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" s="27"/>
       <c r="D29" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="25"/>
@@ -1951,11 +1951,11 @@
         <v>16</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="25"/>
@@ -1984,11 +1984,11 @@
         <v>17</v>
       </c>
       <c r="B31" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C31" s="27"/>
       <c r="D31" s="29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E31" s="27"/>
       <c r="F31" s="25"/>
@@ -2017,11 +2017,11 @@
         <v>18</v>
       </c>
       <c r="B32" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" s="27"/>
       <c r="D32" s="29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E32" s="27"/>
       <c r="F32" s="25"/>
@@ -2050,11 +2050,11 @@
         <v>19</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" s="27"/>
       <c r="D33" s="29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E33" s="27"/>
       <c r="F33" s="25"/>
@@ -2083,11 +2083,11 @@
         <v>20</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="31"/>
       <c r="D34" s="30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E34" s="31"/>
       <c r="F34" s="32"/>
@@ -2116,11 +2116,11 @@
         <v>21</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C35" s="27"/>
       <c r="D35" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E35" s="27"/>
       <c r="F35" s="25"/>
@@ -2149,11 +2149,11 @@
         <v>22</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36" s="31"/>
       <c r="D36" s="30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E36" s="31"/>
       <c r="F36" s="32"/>
